--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3195876288659794</v>
+        <v>0.3814432989690721</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="C2">
-        <v>0.4154929577464789</v>
+        <v>0.4647887323943662</v>
       </c>
       <c r="D2">
-        <v>0.7280701754385965</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E2">
         <v>97</v>
